--- a/public/tools/mitsumori-hikaku.xlsx
+++ b/public/tools/mitsumori-hikaku.xlsx
@@ -519,7 +519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>にいがた実家じまい帖／更新 2026-10-03／登録不要・無料・再配布可（出典明記）。薄い灰色の列は確認の目安、白い欄に記入してください。</t>
+          <t>新潟 実家じまいナビ／更新 2026-10-03／登録不要・無料・再配布可（出典明記）。薄い灰色の列は確認の目安、白い欄に記入してください。</t>
         </is>
       </c>
     </row>
